--- a/Arquivos consulta pessoal/Modelo_Importacao_Confinamento.xlsx
+++ b/Arquivos consulta pessoal/Modelo_Importacao_Confinamento.xlsx
@@ -1,18 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/86d263c7d248ff7d/Área de Trabalho/CLAUDE/Webapp Confinamento/Arquivos consulta pessoal/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_872DA3AADF11254130E572E09F1E73D578F079F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8386F83-FE65-409C-BED7-0B2A28D69767}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LEIA-ME" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Pesagens" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Cadastro_Animais" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="LEIA-ME" sheetId="1" r:id="rId1"/>
+    <sheet name="Pesagens" sheetId="2" r:id="rId2"/>
+    <sheet name="Cadastro_Animais" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -21,13 +26,13 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -35,11 +40,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Formato AAAA-MM-DD, ex.: 2026-08-15</t>
+          <t>Formato AAAA-MM-DD, ex.: 2026-08-15</t>
         </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -47,7 +52,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Para lote AGREGADO (sem brinco), deixe em branco e informe o lote na coluna adicional? Não: agregado é pesado no Cadastro. Aqui é 1 brinco por linha.</t>
+          <t>Para lote AGREGADO (sem brinco), deixe em branco e informe o lote na coluna adicional? Não: agregado é pesado no Cadastro. Aqui é 1 brinco por linha.</t>
         </r>
       </text>
     </comment>
@@ -55,13 +60,13 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -69,12 +74,12 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">individual = 1 animal por linha (com brinco).
+          <t>individual = 1 animal por linha (com brinco).
 agregado = 1 lote por linha (sem brinco, usa Qtd + Peso Médio).</t>
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -82,11 +87,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Só para tipo 'individual'. Deixe vazio no 'agregado'.</t>
+          <t>Só para tipo 'individual'. Deixe vazio no 'agregado'.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -94,11 +99,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Só para tipo 'agregado': número de cabeças do lote.</t>
+          <t>Só para tipo 'agregado': número de cabeças do lote.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -106,7 +111,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Individual: peso do animal.
+          <t>Individual: peso do animal.
 Agregado: peso MÉDIO do lote.</t>
         </r>
       </text>
@@ -116,157 +121,163 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
-    <t xml:space="preserve">COMO USAR ESTE MODELO</t>
+    <t>COMO USAR ESTE MODELO</t>
   </si>
   <si>
-    <t xml:space="preserve">Este arquivo é o formato que o SISTEMA aceita para importar dados.</t>
+    <t>Este arquivo é o formato que o SISTEMA aceita para importar dados.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fluxo: o campo preenche a FOLHA DE CAMPO (papel) → você digitaliza (PDF) →</t>
+    <t>Fluxo: o campo preenche a FOLHA DE CAMPO (papel) → você digitaliza (PDF) →</t>
   </si>
   <si>
-    <t xml:space="preserve">o Cowork converte para este modelo → você sobe este arquivo no sistema.</t>
+    <t>o Cowork converte para este modelo → você sobe este arquivo no sistema.</t>
   </si>
   <si>
-    <t xml:space="preserve">ABAS:</t>
+    <t>ABAS:</t>
   </si>
   <si>
-    <t xml:space="preserve">• Pesagens — uma linha por pesagem (individual, com brinco).</t>
+    <t>• Pesagens — uma linha por pesagem (individual, com brinco).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Cadastro_Animais — entrada de animais novos (individual ou agregado).</t>
+    <t>• Cadastro_Animais — entrada de animais novos (individual ou agregado).</t>
   </si>
   <si>
-    <t xml:space="preserve">REGRAS:</t>
+    <t>REGRAS:</t>
   </si>
   <si>
-    <t xml:space="preserve">• Não altere os nomes dos títulos das colunas.</t>
+    <t>• Não altere os nomes dos títulos das colunas.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Datas sempre no formato AAAA-MM-DD (ex.: 2026-08-15).</t>
+    <t>• Datas sempre no formato AAAA-MM-DD (ex.: 2026-08-15).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Fazenda, Categoria e Curral: use as listas suspensas.</t>
+    <t>• Fazenda, Categoria e Curral: use as listas suspensas.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Células de exemplo (em azul) podem ser apagadas antes de subir.</t>
+    <t>• Células de exemplo (em azul) podem ser apagadas antes de subir.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Pesos e quantidades: apenas números.</t>
+    <t>• Pesos e quantidades: apenas números.</t>
   </si>
   <si>
-    <t xml:space="preserve">As listas de Categoria e Curral neste modelo são uma referência inicial.</t>
+    <t>As listas de Categoria e Curral neste modelo são uma referência inicial.</t>
   </si>
   <si>
-    <t xml:space="preserve">O sistema valida contra o cadastro real de cada fazenda no momento da importação.</t>
+    <t>O sistema valida contra o cadastro real de cada fazenda no momento da importação.</t>
   </si>
   <si>
-    <t xml:space="preserve">MODELO DE IMPORTAÇÃO — PESAGENS</t>
+    <t>MODELO DE IMPORTAÇÃO — PESAGENS</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma linha por pesagem. Preencha a partir da linha 5. Não altere os títulos da linha 4. Data no formato AAAA-MM-DD. Peso em kg (número). Categoria e Curral devem existir no cadastro da fazenda.</t>
+    <t>Uma linha por pesagem. Preencha a partir da linha 5. Não altere os títulos da linha 4. Data no formato AAAA-MM-DD. Peso em kg (número). Categoria e Curral devem existir no cadastro da fazenda.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fazenda</t>
+    <t>Fazenda</t>
   </si>
   <si>
-    <t xml:space="preserve">Data</t>
+    <t>Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Brinco</t>
+    <t>Brinco</t>
   </si>
   <si>
-    <t xml:space="preserve">Categoria</t>
+    <t>Categoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Curral</t>
+    <t>Curral</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso (kg)</t>
+    <t>Peso (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">BG</t>
+    <t>BG</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-15</t>
+    <t>2026-08-15</t>
   </si>
   <si>
-    <t xml:space="preserve">BBG 3339</t>
+    <t>BBG 3339</t>
   </si>
   <si>
-    <t xml:space="preserve">Touro Bonsmara</t>
+    <t>Touro Bonsmara</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
+    <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">↑ linha de exemplo (pode apagar)</t>
+    <t>↑ linha de exemplo (pode apagar)</t>
   </si>
   <si>
-    <t xml:space="preserve">MODELO DE IMPORTAÇÃO — CADASTRO DE ANIMAIS (ENTRADA)</t>
+    <t>MODELO DE IMPORTAÇÃO — CADASTRO DE ANIMAIS (ENTRADA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cadastro de animais que ENTRAM no confinamento. Dois modos:
+    <t>Cadastro de animais que ENTRAM no confinamento. Dois modos:
 • INDIVIDUAL: uma linha por animal, com Brinco e Peso de Entrada.
 • AGREGADO: uma linha por LOTE, sem brinco, informando Quantidade e Peso Médio de Entrada.
 Preencha a partir da linha 6. Data AAAA-MM-DD. Não altere os títulos da linha 5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tipo Entrada</t>
+    <t>Tipo Entrada</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Entrada</t>
+    <t>Data Entrada</t>
   </si>
   <si>
-    <t xml:space="preserve">Lote/Origem</t>
+    <t>Lote/Origem</t>
   </si>
   <si>
-    <t xml:space="preserve">Qtd (agregado)</t>
+    <t>Qtd (agregado)</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso Entrada (kg)</t>
+    <t>Peso Entrada (kg)</t>
   </si>
   <si>
-    <t xml:space="preserve">individual</t>
+    <t>individual</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-30</t>
+    <t>2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Retiro 1</t>
+    <t>Retiro 1</t>
   </si>
   <si>
-    <t xml:space="preserve">PD</t>
+    <t>PD</t>
   </si>
   <si>
-    <t xml:space="preserve">agregado</t>
+    <t>agregado</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-17</t>
+    <t>2026-07-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Boi</t>
+    <t>Boi</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
+    <t>4</t>
   </si>
   <si>
-    <t xml:space="preserve">Compra Fulano</t>
+    <t>Compra Fulano</t>
   </si>
   <si>
-    <t xml:space="preserve">↑ duas linhas de exemplo (individual e agregado — pode apagar)</t>
+    <t>↑ duas linhas de exemplo (individual e agregado — pode apagar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra Marcim </t>
+  </si>
+  <si>
+    <t>Bezerro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,63 +286,42 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF2E5E3A"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="11"/>
       <color rgb="FF1F5FBF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -355,14 +345,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFC9D6CC"/>
       </left>
@@ -378,81 +368,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -511,47 +463,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF2E5E3A"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -559,12 +527,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -593,7 +561,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -614,7 +582,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -665,7 +633,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -683,154 +651,145 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="95"/>
+    <col min="1" max="1" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F204"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F205"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
@@ -850,7 +809,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>23</v>
       </c>
@@ -866,24 +825,36 @@
       <c r="E5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="6">
         <v>548</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="12">
+        <v>46250</v>
+      </c>
+      <c r="C6" s="10">
+        <v>2125</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -891,7 +862,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -899,7 +870,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -907,7 +878,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -915,7 +886,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -923,7 +894,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -931,7 +902,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -939,7 +910,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -947,7 +918,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -955,7 +926,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -963,7 +934,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -971,7 +942,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -979,7 +950,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -987,7 +958,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -995,7 +966,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1003,7 +974,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1011,7 +982,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1019,7 +990,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1027,7 +998,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1035,7 +1006,7 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1043,7 +1014,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1051,7 +1022,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1059,7 +1030,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1067,7 +1038,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1075,7 +1046,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1083,7 +1054,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -1091,7 +1062,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -1099,7 +1070,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1107,7 +1078,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -1115,7 +1086,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -1123,7 +1094,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1131,7 +1102,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1139,7 +1110,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1147,7 +1118,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1155,7 +1126,7 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1163,7 +1134,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1171,7 +1142,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1179,7 +1150,7 @@
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1187,7 +1158,7 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1195,7 +1166,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1203,7 +1174,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -1211,7 +1182,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -1219,7 +1190,7 @@
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1227,7 +1198,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1235,7 +1206,7 @@
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -1243,7 +1214,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -1251,7 +1222,7 @@
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -1259,7 +1230,7 @@
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -1267,7 +1238,7 @@
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -1275,7 +1246,7 @@
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -1283,7 +1254,7 @@
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -1291,7 +1262,7 @@
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
@@ -1299,7 +1270,7 @@
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -1307,7 +1278,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
@@ -1315,7 +1286,7 @@
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -1323,7 +1294,7 @@
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -1331,7 +1302,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -1339,7 +1310,7 @@
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -1347,7 +1318,7 @@
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -1355,7 +1326,7 @@
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -1363,7 +1334,7 @@
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
@@ -1371,7 +1342,7 @@
       <c r="E68" s="9"/>
       <c r="F68" s="9"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
@@ -1379,7 +1350,7 @@
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
@@ -1387,7 +1358,7 @@
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
@@ -1395,7 +1366,7 @@
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -1403,7 +1374,7 @@
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
@@ -1411,7 +1382,7 @@
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -1419,7 +1390,7 @@
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -1427,7 +1398,7 @@
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -1435,7 +1406,7 @@
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -1443,7 +1414,7 @@
       <c r="E77" s="9"/>
       <c r="F77" s="9"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -1451,7 +1422,7 @@
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -1459,7 +1430,7 @@
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
@@ -1467,7 +1438,7 @@
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
@@ -1475,7 +1446,7 @@
       <c r="E81" s="9"/>
       <c r="F81" s="9"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
@@ -1483,7 +1454,7 @@
       <c r="E82" s="9"/>
       <c r="F82" s="9"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -1491,7 +1462,7 @@
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
@@ -1499,7 +1470,7 @@
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
@@ -1507,7 +1478,7 @@
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
@@ -1515,7 +1486,7 @@
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -1523,7 +1494,7 @@
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
@@ -1531,7 +1502,7 @@
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="9"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -1539,7 +1510,7 @@
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -1547,7 +1518,7 @@
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="9"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
@@ -1555,7 +1526,7 @@
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -1563,7 +1534,7 @@
       <c r="E92" s="9"/>
       <c r="F92" s="9"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="9"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -1571,7 +1542,7 @@
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
@@ -1579,7 +1550,7 @@
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="9"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
@@ -1587,7 +1558,7 @@
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
@@ -1595,7 +1566,7 @@
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="9"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
@@ -1603,7 +1574,7 @@
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
@@ -1611,7 +1582,7 @@
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -1619,7 +1590,7 @@
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="9"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
@@ -1627,7 +1598,7 @@
       <c r="E100" s="9"/>
       <c r="F100" s="9"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
@@ -1635,7 +1606,7 @@
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="9"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
@@ -1643,7 +1614,7 @@
       <c r="E102" s="9"/>
       <c r="F102" s="9"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="9"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
@@ -1651,7 +1622,7 @@
       <c r="E103" s="9"/>
       <c r="F103" s="9"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="9"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
@@ -1659,7 +1630,7 @@
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="9"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
@@ -1667,7 +1638,7 @@
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="9"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
@@ -1675,7 +1646,7 @@
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="9"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
@@ -1683,7 +1654,7 @@
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="9"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
@@ -1691,7 +1662,7 @@
       <c r="E108" s="9"/>
       <c r="F108" s="9"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="9"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
@@ -1699,7 +1670,7 @@
       <c r="E109" s="9"/>
       <c r="F109" s="9"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="9"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
@@ -1707,7 +1678,7 @@
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
@@ -1715,7 +1686,7 @@
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="9"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
@@ -1723,7 +1694,7 @@
       <c r="E112" s="9"/>
       <c r="F112" s="9"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="9"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
@@ -1731,7 +1702,7 @@
       <c r="E113" s="9"/>
       <c r="F113" s="9"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="9"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -1739,7 +1710,7 @@
       <c r="E114" s="9"/>
       <c r="F114" s="9"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="9"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
@@ -1747,7 +1718,7 @@
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="9"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -1755,7 +1726,7 @@
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="9"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -1763,7 +1734,7 @@
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="9"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
@@ -1771,7 +1742,7 @@
       <c r="E118" s="9"/>
       <c r="F118" s="9"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="9"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
@@ -1779,7 +1750,7 @@
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="9"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
@@ -1787,7 +1758,7 @@
       <c r="E120" s="9"/>
       <c r="F120" s="9"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="9"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
@@ -1795,7 +1766,7 @@
       <c r="E121" s="9"/>
       <c r="F121" s="9"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="9"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -1803,7 +1774,7 @@
       <c r="E122" s="9"/>
       <c r="F122" s="9"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -1811,7 +1782,7 @@
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
@@ -1819,7 +1790,7 @@
       <c r="E124" s="9"/>
       <c r="F124" s="9"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
@@ -1827,7 +1798,7 @@
       <c r="E125" s="9"/>
       <c r="F125" s="9"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -1835,7 +1806,7 @@
       <c r="E126" s="9"/>
       <c r="F126" s="9"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
@@ -1843,7 +1814,7 @@
       <c r="E127" s="9"/>
       <c r="F127" s="9"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
@@ -1851,7 +1822,7 @@
       <c r="E128" s="9"/>
       <c r="F128" s="9"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -1859,7 +1830,7 @@
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="9"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
@@ -1867,7 +1838,7 @@
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
@@ -1875,7 +1846,7 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="9"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -1883,7 +1854,7 @@
       <c r="E132" s="9"/>
       <c r="F132" s="9"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="9"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
@@ -1891,7 +1862,7 @@
       <c r="E133" s="9"/>
       <c r="F133" s="9"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="9"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
@@ -1899,7 +1870,7 @@
       <c r="E134" s="9"/>
       <c r="F134" s="9"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -1907,7 +1878,7 @@
       <c r="E135" s="9"/>
       <c r="F135" s="9"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="9"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
@@ -1915,7 +1886,7 @@
       <c r="E136" s="9"/>
       <c r="F136" s="9"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
@@ -1923,7 +1894,7 @@
       <c r="E137" s="9"/>
       <c r="F137" s="9"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="9"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
@@ -1931,7 +1902,7 @@
       <c r="E138" s="9"/>
       <c r="F138" s="9"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
@@ -1939,7 +1910,7 @@
       <c r="E139" s="9"/>
       <c r="F139" s="9"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="9"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
@@ -1947,7 +1918,7 @@
       <c r="E140" s="9"/>
       <c r="F140" s="9"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="9"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
@@ -1955,7 +1926,7 @@
       <c r="E141" s="9"/>
       <c r="F141" s="9"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="9"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
@@ -1963,7 +1934,7 @@
       <c r="E142" s="9"/>
       <c r="F142" s="9"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
@@ -1971,7 +1942,7 @@
       <c r="E143" s="9"/>
       <c r="F143" s="9"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="9"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
@@ -1979,7 +1950,7 @@
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="9"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
@@ -1987,7 +1958,7 @@
       <c r="E145" s="9"/>
       <c r="F145" s="9"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="9"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
@@ -1995,7 +1966,7 @@
       <c r="E146" s="9"/>
       <c r="F146" s="9"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
@@ -2003,7 +1974,7 @@
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="9"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
@@ -2011,7 +1982,7 @@
       <c r="E148" s="9"/>
       <c r="F148" s="9"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
@@ -2019,7 +1990,7 @@
       <c r="E149" s="9"/>
       <c r="F149" s="9"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -2027,7 +1998,7 @@
       <c r="E150" s="9"/>
       <c r="F150" s="9"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
@@ -2035,7 +2006,7 @@
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
@@ -2043,7 +2014,7 @@
       <c r="E152" s="9"/>
       <c r="F152" s="9"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
@@ -2051,7 +2022,7 @@
       <c r="E153" s="9"/>
       <c r="F153" s="9"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
@@ -2059,7 +2030,7 @@
       <c r="E154" s="9"/>
       <c r="F154" s="9"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
@@ -2067,7 +2038,7 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
@@ -2075,7 +2046,7 @@
       <c r="E156" s="9"/>
       <c r="F156" s="9"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="9"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
@@ -2083,7 +2054,7 @@
       <c r="E157" s="9"/>
       <c r="F157" s="9"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="9"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
@@ -2091,7 +2062,7 @@
       <c r="E158" s="9"/>
       <c r="F158" s="9"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
@@ -2099,7 +2070,7 @@
       <c r="E159" s="9"/>
       <c r="F159" s="9"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="9"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
@@ -2107,7 +2078,7 @@
       <c r="E160" s="9"/>
       <c r="F160" s="9"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="9"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
@@ -2115,7 +2086,7 @@
       <c r="E161" s="9"/>
       <c r="F161" s="9"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="9"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
@@ -2123,7 +2094,7 @@
       <c r="E162" s="9"/>
       <c r="F162" s="9"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -2131,7 +2102,7 @@
       <c r="E163" s="9"/>
       <c r="F163" s="9"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="9"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
@@ -2139,7 +2110,7 @@
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
@@ -2147,7 +2118,7 @@
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="9"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
@@ -2155,7 +2126,7 @@
       <c r="E166" s="9"/>
       <c r="F166" s="9"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
@@ -2163,7 +2134,7 @@
       <c r="E167" s="9"/>
       <c r="F167" s="9"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="9"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
@@ -2171,7 +2142,7 @@
       <c r="E168" s="9"/>
       <c r="F168" s="9"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
@@ -2179,7 +2150,7 @@
       <c r="E169" s="9"/>
       <c r="F169" s="9"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="9"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
@@ -2187,7 +2158,7 @@
       <c r="E170" s="9"/>
       <c r="F170" s="9"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
@@ -2195,7 +2166,7 @@
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="9"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
@@ -2203,7 +2174,7 @@
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="9"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
@@ -2211,7 +2182,7 @@
       <c r="E173" s="9"/>
       <c r="F173" s="9"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="9"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
@@ -2219,7 +2190,7 @@
       <c r="E174" s="9"/>
       <c r="F174" s="9"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="9"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
@@ -2227,7 +2198,7 @@
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="9"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
@@ -2235,7 +2206,7 @@
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="9"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -2243,7 +2214,7 @@
       <c r="E177" s="9"/>
       <c r="F177" s="9"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="9"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
@@ -2251,7 +2222,7 @@
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="9"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
@@ -2259,7 +2230,7 @@
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="9"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
@@ -2267,7 +2238,7 @@
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="9"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
@@ -2275,7 +2246,7 @@
       <c r="E181" s="9"/>
       <c r="F181" s="9"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="9"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
@@ -2283,7 +2254,7 @@
       <c r="E182" s="9"/>
       <c r="F182" s="9"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="9"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
@@ -2291,7 +2262,7 @@
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="9"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
@@ -2299,7 +2270,7 @@
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="9"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
@@ -2307,7 +2278,7 @@
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="9"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
@@ -2315,7 +2286,7 @@
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="9"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
@@ -2323,7 +2294,7 @@
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -2331,7 +2302,7 @@
       <c r="E188" s="9"/>
       <c r="F188" s="9"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="9"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -2339,7 +2310,7 @@
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="9"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
@@ -2347,7 +2318,7 @@
       <c r="E190" s="9"/>
       <c r="F190" s="9"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
@@ -2355,7 +2326,7 @@
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
@@ -2363,7 +2334,7 @@
       <c r="E192" s="9"/>
       <c r="F192" s="9"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
@@ -2371,7 +2342,7 @@
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
@@ -2379,7 +2350,7 @@
       <c r="E194" s="9"/>
       <c r="F194" s="9"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
@@ -2387,7 +2358,7 @@
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="9"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
@@ -2395,7 +2366,7 @@
       <c r="E196" s="9"/>
       <c r="F196" s="9"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="9"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -2403,7 +2374,7 @@
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="9"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
@@ -2411,7 +2382,7 @@
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -2419,7 +2390,7 @@
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -2427,7 +2398,7 @@
       <c r="E200" s="9"/>
       <c r="F200" s="9"/>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
@@ -2435,7 +2406,7 @@
       <c r="E201" s="9"/>
       <c r="F201" s="9"/>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
@@ -2443,7 +2414,7 @@
       <c r="E202" s="9"/>
       <c r="F202" s="9"/>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
@@ -2451,7 +2422,7 @@
       <c r="E203" s="9"/>
       <c r="F203" s="9"/>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="9"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -2459,76 +2430,76 @@
       <c r="E204" s="9"/>
       <c r="F204" s="9"/>
     </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A5:A1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="A5:A1001" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"BG,PD"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="D5:D1001" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Touro Bonsmara,Touro Nelore,Bezerro,Novilha Nelore,Touro Bonsmara Descarte,Boi,F Cruz. Industrial"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="E5:E1001" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"1,2,3,4,5,6,7,8,9,10,4-TN,(a definir)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Digite um número maior que 0." errorStyle="stop" errorTitle="Número inválido" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F1000" type="decimal">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" errorTitle="Número inválido" error="Digite um número maior que 0." sqref="F5:F1001" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I208"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I209"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -2557,7 +2528,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -2580,11 +2551,11 @@
         <v>38</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="6">
         <v>670</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>39</v>
       </c>
@@ -2604,30 +2575,44 @@
       <c r="G7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="6">
         <v>90</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="6">
         <v>385</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="12">
+        <v>46346</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2122</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -2638,7 +2623,7 @@
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2649,7 +2634,7 @@
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2660,7 +2645,7 @@
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -2671,7 +2656,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -2682,7 +2667,7 @@
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -2693,7 +2678,7 @@
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -2704,7 +2689,7 @@
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -2715,7 +2700,7 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -2726,7 +2711,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -2737,7 +2722,7 @@
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -2748,7 +2733,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -2759,7 +2744,7 @@
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2770,7 +2755,7 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -2781,7 +2766,7 @@
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -2792,7 +2777,7 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2803,7 +2788,7 @@
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2814,7 +2799,7 @@
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -2825,7 +2810,7 @@
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -2836,7 +2821,7 @@
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -2847,7 +2832,7 @@
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2858,7 +2843,7 @@
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -2869,7 +2854,7 @@
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -2880,7 +2865,7 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -2891,7 +2876,7 @@
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2902,7 +2887,7 @@
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -2913,7 +2898,7 @@
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -2924,7 +2909,7 @@
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -2935,7 +2920,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -2946,7 +2931,7 @@
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2957,7 +2942,7 @@
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -2968,7 +2953,7 @@
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -2979,7 +2964,7 @@
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -2990,7 +2975,7 @@
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -3001,7 +2986,7 @@
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -3012,7 +2997,7 @@
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -3023,7 +3008,7 @@
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -3034,7 +3019,7 @@
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -3045,7 +3030,7 @@
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -3056,7 +3041,7 @@
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -3067,7 +3052,7 @@
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -3078,7 +3063,7 @@
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -3089,7 +3074,7 @@
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -3100,7 +3085,7 @@
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -3111,7 +3096,7 @@
       <c r="H53" s="9"/>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -3122,7 +3107,7 @@
       <c r="H54" s="9"/>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -3133,7 +3118,7 @@
       <c r="H55" s="9"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -3144,7 +3129,7 @@
       <c r="H56" s="9"/>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -3155,7 +3140,7 @@
       <c r="H57" s="9"/>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -3166,7 +3151,7 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
@@ -3177,7 +3162,7 @@
       <c r="H59" s="9"/>
       <c r="I59" s="9"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -3188,7 +3173,7 @@
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
@@ -3199,7 +3184,7 @@
       <c r="H61" s="9"/>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -3210,7 +3195,7 @@
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -3221,7 +3206,7 @@
       <c r="H63" s="9"/>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -3232,7 +3217,7 @@
       <c r="H64" s="9"/>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -3243,7 +3228,7 @@
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -3254,7 +3239,7 @@
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -3265,7 +3250,7 @@
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
@@ -3276,7 +3261,7 @@
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
@@ -3287,7 +3272,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
@@ -3298,7 +3283,7 @@
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
@@ -3309,7 +3294,7 @@
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -3320,7 +3305,7 @@
       <c r="H72" s="9"/>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
@@ -3331,7 +3316,7 @@
       <c r="H73" s="9"/>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -3342,7 +3327,7 @@
       <c r="H74" s="9"/>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -3353,7 +3338,7 @@
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -3364,7 +3349,7 @@
       <c r="H76" s="9"/>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -3375,7 +3360,7 @@
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -3386,7 +3371,7 @@
       <c r="H78" s="9"/>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -3397,7 +3382,7 @@
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
@@ -3408,7 +3393,7 @@
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
@@ -3419,7 +3404,7 @@
       <c r="H81" s="9"/>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
@@ -3430,7 +3415,7 @@
       <c r="H82" s="9"/>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -3441,7 +3426,7 @@
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
@@ -3452,7 +3437,7 @@
       <c r="H84" s="9"/>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
@@ -3463,7 +3448,7 @@
       <c r="H85" s="9"/>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
@@ -3474,7 +3459,7 @@
       <c r="H86" s="9"/>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -3485,7 +3470,7 @@
       <c r="H87" s="9"/>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
@@ -3496,7 +3481,7 @@
       <c r="H88" s="9"/>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="9"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3507,7 +3492,7 @@
       <c r="H89" s="9"/>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -3518,7 +3503,7 @@
       <c r="H90" s="9"/>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="9"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
@@ -3529,7 +3514,7 @@
       <c r="H91" s="9"/>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -3540,7 +3525,7 @@
       <c r="H92" s="9"/>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="9"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -3551,7 +3536,7 @@
       <c r="H93" s="9"/>
       <c r="I93" s="9"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
@@ -3562,7 +3547,7 @@
       <c r="H94" s="9"/>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="9"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
@@ -3573,7 +3558,7 @@
       <c r="H95" s="9"/>
       <c r="I95" s="9"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
@@ -3584,7 +3569,7 @@
       <c r="H96" s="9"/>
       <c r="I96" s="9"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="9"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
@@ -3595,7 +3580,7 @@
       <c r="H97" s="9"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
@@ -3606,7 +3591,7 @@
       <c r="H98" s="9"/>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -3617,7 +3602,7 @@
       <c r="H99" s="9"/>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="9"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
@@ -3628,7 +3613,7 @@
       <c r="H100" s="9"/>
       <c r="I100" s="9"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
@@ -3639,7 +3624,7 @@
       <c r="H101" s="9"/>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="9"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
@@ -3650,7 +3635,7 @@
       <c r="H102" s="9"/>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="9"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
@@ -3661,7 +3646,7 @@
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="9"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
@@ -3672,7 +3657,7 @@
       <c r="H104" s="9"/>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="9"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
@@ -3683,7 +3668,7 @@
       <c r="H105" s="9"/>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="9"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
@@ -3694,7 +3679,7 @@
       <c r="H106" s="9"/>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="9"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
@@ -3705,7 +3690,7 @@
       <c r="H107" s="9"/>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="9"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
@@ -3716,7 +3701,7 @@
       <c r="H108" s="9"/>
       <c r="I108" s="9"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="9"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
@@ -3727,7 +3712,7 @@
       <c r="H109" s="9"/>
       <c r="I109" s="9"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="9"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
@@ -3738,7 +3723,7 @@
       <c r="H110" s="9"/>
       <c r="I110" s="9"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
@@ -3749,7 +3734,7 @@
       <c r="H111" s="9"/>
       <c r="I111" s="9"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="9"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
@@ -3760,7 +3745,7 @@
       <c r="H112" s="9"/>
       <c r="I112" s="9"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="9"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
@@ -3771,7 +3756,7 @@
       <c r="H113" s="9"/>
       <c r="I113" s="9"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="9"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -3782,7 +3767,7 @@
       <c r="H114" s="9"/>
       <c r="I114" s="9"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="9"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
@@ -3793,7 +3778,7 @@
       <c r="H115" s="9"/>
       <c r="I115" s="9"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="9"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -3804,7 +3789,7 @@
       <c r="H116" s="9"/>
       <c r="I116" s="9"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="9"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -3815,7 +3800,7 @@
       <c r="H117" s="9"/>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="9"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
@@ -3826,7 +3811,7 @@
       <c r="H118" s="9"/>
       <c r="I118" s="9"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="9"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
@@ -3837,7 +3822,7 @@
       <c r="H119" s="9"/>
       <c r="I119" s="9"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="9"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
@@ -3848,7 +3833,7 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="9"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
@@ -3859,7 +3844,7 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="9"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -3870,7 +3855,7 @@
       <c r="H122" s="9"/>
       <c r="I122" s="9"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -3881,7 +3866,7 @@
       <c r="H123" s="9"/>
       <c r="I123" s="9"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
@@ -3892,7 +3877,7 @@
       <c r="H124" s="9"/>
       <c r="I124" s="9"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
@@ -3903,7 +3888,7 @@
       <c r="H125" s="9"/>
       <c r="I125" s="9"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -3914,7 +3899,7 @@
       <c r="H126" s="9"/>
       <c r="I126" s="9"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
@@ -3925,7 +3910,7 @@
       <c r="H127" s="9"/>
       <c r="I127" s="9"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
@@ -3936,7 +3921,7 @@
       <c r="H128" s="9"/>
       <c r="I128" s="9"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -3947,7 +3932,7 @@
       <c r="H129" s="9"/>
       <c r="I129" s="9"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="9"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
@@ -3958,7 +3943,7 @@
       <c r="H130" s="9"/>
       <c r="I130" s="9"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
@@ -3969,7 +3954,7 @@
       <c r="H131" s="9"/>
       <c r="I131" s="9"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="9"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -3980,7 +3965,7 @@
       <c r="H132" s="9"/>
       <c r="I132" s="9"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="9"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
@@ -3991,7 +3976,7 @@
       <c r="H133" s="9"/>
       <c r="I133" s="9"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="9"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
@@ -4002,7 +3987,7 @@
       <c r="H134" s="9"/>
       <c r="I134" s="9"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -4013,7 +3998,7 @@
       <c r="H135" s="9"/>
       <c r="I135" s="9"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="9"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
@@ -4024,7 +4009,7 @@
       <c r="H136" s="9"/>
       <c r="I136" s="9"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
@@ -4035,7 +4020,7 @@
       <c r="H137" s="9"/>
       <c r="I137" s="9"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="9"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
@@ -4046,7 +4031,7 @@
       <c r="H138" s="9"/>
       <c r="I138" s="9"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
@@ -4057,7 +4042,7 @@
       <c r="H139" s="9"/>
       <c r="I139" s="9"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="9"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
@@ -4068,7 +4053,7 @@
       <c r="H140" s="9"/>
       <c r="I140" s="9"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="9"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
@@ -4079,7 +4064,7 @@
       <c r="H141" s="9"/>
       <c r="I141" s="9"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="9"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
@@ -4090,7 +4075,7 @@
       <c r="H142" s="9"/>
       <c r="I142" s="9"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
@@ -4101,7 +4086,7 @@
       <c r="H143" s="9"/>
       <c r="I143" s="9"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="9"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
@@ -4112,7 +4097,7 @@
       <c r="H144" s="9"/>
       <c r="I144" s="9"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="9"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
@@ -4123,7 +4108,7 @@
       <c r="H145" s="9"/>
       <c r="I145" s="9"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="9"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
@@ -4134,7 +4119,7 @@
       <c r="H146" s="9"/>
       <c r="I146" s="9"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
@@ -4145,7 +4130,7 @@
       <c r="H147" s="9"/>
       <c r="I147" s="9"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="9"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
@@ -4156,7 +4141,7 @@
       <c r="H148" s="9"/>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
@@ -4167,7 +4152,7 @@
       <c r="H149" s="9"/>
       <c r="I149" s="9"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -4178,7 +4163,7 @@
       <c r="H150" s="9"/>
       <c r="I150" s="9"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
@@ -4189,7 +4174,7 @@
       <c r="H151" s="9"/>
       <c r="I151" s="9"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
@@ -4200,7 +4185,7 @@
       <c r="H152" s="9"/>
       <c r="I152" s="9"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
@@ -4211,7 +4196,7 @@
       <c r="H153" s="9"/>
       <c r="I153" s="9"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
@@ -4222,7 +4207,7 @@
       <c r="H154" s="9"/>
       <c r="I154" s="9"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
@@ -4233,7 +4218,7 @@
       <c r="H155" s="9"/>
       <c r="I155" s="9"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
@@ -4244,7 +4229,7 @@
       <c r="H156" s="9"/>
       <c r="I156" s="9"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="9"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
@@ -4255,7 +4240,7 @@
       <c r="H157" s="9"/>
       <c r="I157" s="9"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="9"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
@@ -4266,7 +4251,7 @@
       <c r="H158" s="9"/>
       <c r="I158" s="9"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
@@ -4277,7 +4262,7 @@
       <c r="H159" s="9"/>
       <c r="I159" s="9"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="9"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
@@ -4288,7 +4273,7 @@
       <c r="H160" s="9"/>
       <c r="I160" s="9"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="9"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
@@ -4299,7 +4284,7 @@
       <c r="H161" s="9"/>
       <c r="I161" s="9"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="9"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
@@ -4310,7 +4295,7 @@
       <c r="H162" s="9"/>
       <c r="I162" s="9"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -4321,7 +4306,7 @@
       <c r="H163" s="9"/>
       <c r="I163" s="9"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="9"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
@@ -4332,7 +4317,7 @@
       <c r="H164" s="9"/>
       <c r="I164" s="9"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
@@ -4343,7 +4328,7 @@
       <c r="H165" s="9"/>
       <c r="I165" s="9"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="9"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
@@ -4354,7 +4339,7 @@
       <c r="H166" s="9"/>
       <c r="I166" s="9"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
@@ -4365,7 +4350,7 @@
       <c r="H167" s="9"/>
       <c r="I167" s="9"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="9"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
@@ -4376,7 +4361,7 @@
       <c r="H168" s="9"/>
       <c r="I168" s="9"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
@@ -4387,7 +4372,7 @@
       <c r="H169" s="9"/>
       <c r="I169" s="9"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="9"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
@@ -4398,7 +4383,7 @@
       <c r="H170" s="9"/>
       <c r="I170" s="9"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="9"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
@@ -4409,7 +4394,7 @@
       <c r="H171" s="9"/>
       <c r="I171" s="9"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="9"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
@@ -4420,7 +4405,7 @@
       <c r="H172" s="9"/>
       <c r="I172" s="9"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="9"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
@@ -4431,7 +4416,7 @@
       <c r="H173" s="9"/>
       <c r="I173" s="9"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="9"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
@@ -4442,7 +4427,7 @@
       <c r="H174" s="9"/>
       <c r="I174" s="9"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="9"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
@@ -4453,7 +4438,7 @@
       <c r="H175" s="9"/>
       <c r="I175" s="9"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="9"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
@@ -4464,7 +4449,7 @@
       <c r="H176" s="9"/>
       <c r="I176" s="9"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="9"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -4475,7 +4460,7 @@
       <c r="H177" s="9"/>
       <c r="I177" s="9"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="9"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
@@ -4486,7 +4471,7 @@
       <c r="H178" s="9"/>
       <c r="I178" s="9"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="9"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
@@ -4497,7 +4482,7 @@
       <c r="H179" s="9"/>
       <c r="I179" s="9"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="9"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
@@ -4508,7 +4493,7 @@
       <c r="H180" s="9"/>
       <c r="I180" s="9"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="9"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
@@ -4519,7 +4504,7 @@
       <c r="H181" s="9"/>
       <c r="I181" s="9"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="9"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
@@ -4530,7 +4515,7 @@
       <c r="H182" s="9"/>
       <c r="I182" s="9"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="9"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
@@ -4541,7 +4526,7 @@
       <c r="H183" s="9"/>
       <c r="I183" s="9"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="9"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
@@ -4552,7 +4537,7 @@
       <c r="H184" s="9"/>
       <c r="I184" s="9"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="9"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
@@ -4563,7 +4548,7 @@
       <c r="H185" s="9"/>
       <c r="I185" s="9"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="9"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
@@ -4574,7 +4559,7 @@
       <c r="H186" s="9"/>
       <c r="I186" s="9"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="9"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
@@ -4585,7 +4570,7 @@
       <c r="H187" s="9"/>
       <c r="I187" s="9"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="9"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -4596,7 +4581,7 @@
       <c r="H188" s="9"/>
       <c r="I188" s="9"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="9"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -4607,7 +4592,7 @@
       <c r="H189" s="9"/>
       <c r="I189" s="9"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="9"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
@@ -4618,7 +4603,7 @@
       <c r="H190" s="9"/>
       <c r="I190" s="9"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
@@ -4629,7 +4614,7 @@
       <c r="H191" s="9"/>
       <c r="I191" s="9"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
@@ -4640,7 +4625,7 @@
       <c r="H192" s="9"/>
       <c r="I192" s="9"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
@@ -4651,7 +4636,7 @@
       <c r="H193" s="9"/>
       <c r="I193" s="9"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
@@ -4662,7 +4647,7 @@
       <c r="H194" s="9"/>
       <c r="I194" s="9"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
@@ -4673,7 +4658,7 @@
       <c r="H195" s="9"/>
       <c r="I195" s="9"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="9"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
@@ -4684,7 +4669,7 @@
       <c r="H196" s="9"/>
       <c r="I196" s="9"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="9"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -4695,7 +4680,7 @@
       <c r="H197" s="9"/>
       <c r="I197" s="9"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="9"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
@@ -4706,7 +4691,7 @@
       <c r="H198" s="9"/>
       <c r="I198" s="9"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="9"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -4717,7 +4702,7 @@
       <c r="H199" s="9"/>
       <c r="I199" s="9"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -4728,7 +4713,7 @@
       <c r="H200" s="9"/>
       <c r="I200" s="9"/>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
@@ -4739,7 +4724,7 @@
       <c r="H201" s="9"/>
       <c r="I201" s="9"/>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
@@ -4750,7 +4735,7 @@
       <c r="H202" s="9"/>
       <c r="I202" s="9"/>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
@@ -4761,7 +4746,7 @@
       <c r="H203" s="9"/>
       <c r="I203" s="9"/>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="9"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -4772,7 +4757,7 @@
       <c r="H204" s="9"/>
       <c r="I204" s="9"/>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="9"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
@@ -4783,7 +4768,7 @@
       <c r="H205" s="9"/>
       <c r="I205" s="9"/>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="9"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
@@ -4794,7 +4779,7 @@
       <c r="H206" s="9"/>
       <c r="I206" s="9"/>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="9"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
@@ -4805,7 +4790,7 @@
       <c r="H207" s="9"/>
       <c r="I207" s="9"/>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="9"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
@@ -4816,39 +4801,45 @@
       <c r="H208" s="9"/>
       <c r="I208" s="9"/>
     </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A209" s="9"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
+      <c r="F209" s="9"/>
+      <c r="G209" s="9"/>
+      <c r="H209" s="9"/>
+      <c r="I209" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation allowBlank="true" error="Digite um número maior que 0." errorStyle="stop" errorTitle="Número inválido" operator="greaterThan" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H6:I1000" type="decimal">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" errorTitle="Número inválido" error="Digite um número maior que 0." sqref="H6:I1001" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A6:A1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="A6:A1001" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"BG,PD"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6:B1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="B6:B1001" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"individual,agregado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:E1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="E6:E1001" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"Touro Bonsmara,Touro Nelore,Bezerro,Novilha Nelore,Touro Bonsmara Descarte,Boi,F Cruz. Industrial"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha um valor da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F6:F1000" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." sqref="F6:F1001" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"1,2,3,4,5,6,7,8,9,10,4-TN,(a definir)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>